--- a/artfynd/A 18539-2024 artfynd.xlsx
+++ b/artfynd/A 18539-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118654383</v>
+        <v>118654372</v>
       </c>
       <c r="B2" t="n">
-        <v>5186</v>
+        <v>5166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655782</v>
+        <v>655993</v>
       </c>
       <c r="R2" t="n">
-        <v>6683564</v>
+        <v>6683573</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118654372</v>
+        <v>118654383</v>
       </c>
       <c r="B3" t="n">
-        <v>5166</v>
+        <v>5186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655993</v>
+        <v>655782</v>
       </c>
       <c r="R3" t="n">
-        <v>6683573</v>
+        <v>6683564</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18539-2024 artfynd.xlsx
+++ b/artfynd/A 18539-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118654372</v>
+        <v>118654374</v>
       </c>
       <c r="B2" t="n">
         <v>5166</v>
@@ -714,7 +714,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655993</v>
+        <v>655788</v>
       </c>
       <c r="R2" t="n">
-        <v>6683573</v>
+        <v>6683563</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118654374</v>
+        <v>118654372</v>
       </c>
       <c r="B4" t="n">
         <v>5166</v>
@@ -956,7 +956,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655788</v>
+        <v>655993</v>
       </c>
       <c r="R4" t="n">
-        <v>6683563</v>
+        <v>6683573</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18539-2024 artfynd.xlsx
+++ b/artfynd/A 18539-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118654374</v>
+        <v>118654383</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
+        <v>5186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,7 +714,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655788</v>
+        <v>655782</v>
       </c>
       <c r="R2" t="n">
-        <v>6683563</v>
+        <v>6683564</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118654383</v>
+        <v>118654374</v>
       </c>
       <c r="B3" t="n">
-        <v>5186</v>
+        <v>5166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,7 +835,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655782</v>
+        <v>655788</v>
       </c>
       <c r="R3" t="n">
-        <v>6683564</v>
+        <v>6683563</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18539-2024 artfynd.xlsx
+++ b/artfynd/A 18539-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118654374</v>
+        <v>118654372</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,7 +709,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655788</v>
+        <v>655993</v>
       </c>
       <c r="R2" t="n">
-        <v>6683563</v>
+        <v>6683573</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118654383</v>
+        <v>118654374</v>
       </c>
       <c r="B3" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,7 +825,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655782</v>
+        <v>655788</v>
       </c>
       <c r="R3" t="n">
-        <v>6683564</v>
+        <v>6683563</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -880,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118654372</v>
+        <v>118654383</v>
       </c>
       <c r="B4" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655993</v>
+        <v>655782</v>
       </c>
       <c r="R4" t="n">
-        <v>6683573</v>
+        <v>6683564</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18539-2024 artfynd.xlsx
+++ b/artfynd/A 18539-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118654372</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118654374</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118654383</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>